--- a/customers_test.xlsx
+++ b/customers_test.xlsx
@@ -20,36 +20,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t xml:space="preserve">الرقم</t>
   </si>
   <si>
+    <t xml:space="preserve">رقم الهوية</t>
+  </si>
+  <si>
     <t xml:space="preserve">الاسم</t>
   </si>
   <si>
+    <t xml:space="preserve">رقم الجوال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عدد افراد الاسرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المسجد</t>
+  </si>
+  <si>
     <t xml:space="preserve">البيان</t>
   </si>
   <si>
     <t xml:space="preserve">سلام ابووردة</t>
   </si>
   <si>
+    <t xml:space="preserve">0599256315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مسجد القططي</t>
+  </si>
+  <si>
     <t xml:space="preserve">سيبالسيلسي</t>
   </si>
   <si>
     <t xml:space="preserve">تسنيم ابو ووردة</t>
   </si>
   <si>
+    <t xml:space="preserve">0599986522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مسجد الفلاح</t>
+  </si>
+  <si>
     <t xml:space="preserve">سيلاسفىيفغةغع</t>
   </si>
   <si>
     <t xml:space="preserve">اسماعيل الددح</t>
   </si>
   <si>
+    <t xml:space="preserve">0592684987</t>
+  </si>
+  <si>
     <t xml:space="preserve">ةوغهولعخزمعلهنعفتيىفي</t>
   </si>
   <si>
     <t xml:space="preserve">محمود عزمي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0562563651</t>
   </si>
   <si>
     <t xml:space="preserve">فيغتقغافتفغت</t>
@@ -59,9 +89,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -147,7 +178,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -156,15 +187,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -295,74 +338,131 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="12.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="4" t="n">
+        <v>859652365</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>425632685</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B4" s="4" t="n">
+        <v>965231459</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="n">
+        <v>401256385</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3"/>
+      <c r="G5" s="8" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0"/>
+      <c r="B6" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
